--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1268,58 +1268,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73477765</v>
+        <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>93235</v>
+        <v>92078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sylbergen SO, Vstm</t>
+          <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558527</v>
+        <v>558672</v>
       </c>
       <c r="R7" t="n">
-        <v>6632099</v>
+        <v>6632439</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1343,12 +1336,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-10-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-10-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,7 +1356,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1380,13 +1378,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73477765</t>
+          <t>https://artportalen.se/Sighting/137037851</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75153254</v>
+        <v>73477765</v>
       </c>
       <c r="B8" t="n">
         <v>93235</v>
@@ -1416,7 +1414,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1425,20 +1423,19 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Sylbergen SO, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558307</v>
+        <v>558527</v>
       </c>
       <c r="R8" t="n">
-        <v>6632318</v>
+        <v>6632099</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,12 +1459,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,7 +1479,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1499,13 +1496,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75153254</t>
+          <t>https://artportalen.se/Sighting/73477765</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96226860</v>
+        <v>75153254</v>
       </c>
       <c r="B9" t="n">
         <v>93235</v>
@@ -1535,7 +1532,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1551,13 +1548,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558519</v>
+        <v>558307</v>
       </c>
       <c r="R9" t="n">
-        <v>6632262</v>
+        <v>6632318</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,12 +1578,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,30 +1598,30 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96226860</t>
+          <t>https://artportalen.se/Sighting/75153254</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120085780</v>
+        <v>96226860</v>
       </c>
       <c r="B10" t="n">
         <v>93235</v>
@@ -1657,19 +1654,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm , Sylbergen, Ramnäs, Vstm , Vstm</t>
+          <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558268</v>
+        <v>558519</v>
       </c>
       <c r="R10" t="n">
-        <v>6632211</v>
+        <v>6632262</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1693,22 +1697,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,35 +1711,36 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120085780</t>
+          <t>https://artportalen.se/Sighting/96226860</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485458</v>
+        <v>120085780</v>
       </c>
       <c r="B11" t="n">
         <v>93235</v>
@@ -1773,20 +1768,24 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm , Sylbergen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558213</v>
+        <v>558268</v>
       </c>
       <c r="R11" t="n">
-        <v>6632315</v>
+        <v>6632211</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1810,12 +1809,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,89 +1836,73 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122485458</t>
+          <t>https://artportalen.se/Sighting/120085780</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131851698</v>
+        <v>122485458</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm, Sylbergen, Ramnäs, Vstm, Vstm</t>
+          <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558412</v>
+        <v>558213</v>
       </c>
       <c r="R12" t="n">
-        <v>6632166</v>
+        <v>6632315</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1933,22 +1926,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,81 +1943,88 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131851698</t>
+          <t>https://artportalen.se/Sighting/122485458</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>84232189</v>
+        <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>57141</v>
+        <v>93451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ö Sylbergen, Ramnäs, Vstm, Vstm</t>
+          <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558625</v>
+        <v>558481</v>
       </c>
       <c r="R13" t="n">
-        <v>6632319</v>
+        <v>6632215</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2058,27 +2048,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-04-07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-04-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>En fjäder från tjäder i skogsområde med tjäderspillning</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,93 +2062,88 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Hällmarker med gran och tallskog, blåbärsris.</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84232189</t>
+          <t>https://artportalen.se/Sighting/137037232</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>83846738</v>
+        <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>57144</v>
+        <v>93451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm, Vstm</t>
+          <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558224</v>
+        <v>558591</v>
       </c>
       <c r="R14" t="n">
-        <v>6632361</v>
+        <v>6632359</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2197,22 +2167,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-03-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-03-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>5+2</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,43 +2186,39 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Tall och gran på hällmark</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83846738</t>
+          <t>https://artportalen.se/Sighting/137037708</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102829427</v>
+        <v>131851698</v>
       </c>
       <c r="B15" t="n">
-        <v>58439</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,41 +2226,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2309,17 +2258,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Målsjövägen, Ramnäs, Vstm, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm, Sylbergen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558653</v>
+        <v>558412</v>
       </c>
       <c r="R15" t="n">
-        <v>6632198</v>
+        <v>6632166</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2343,22 +2292,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2386,70 +2335,65 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102829427</t>
+          <t>https://artportalen.se/Sighting/131851698</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132490733</v>
+        <v>84232189</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm, Sylbergen, Ramnäs, Vstm, Vstm</t>
+          <t>Ö Sylbergen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558136</v>
+        <v>558625</v>
       </c>
       <c r="R16" t="n">
-        <v>6632414</v>
+        <v>6632319</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2473,22 +2417,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2020-04-07</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2020-04-07</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En fjäder från tjäder i skogsområde med tjäderspillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2502,7 +2451,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Häll- och blockskog</t>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Hällmarker med gran och tallskog, blåbärsris.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2519,63 +2473,66 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132490733</t>
+          <t>https://artportalen.se/Sighting/84232189</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135762156</v>
+        <v>83846738</v>
       </c>
       <c r="B17" t="n">
-        <v>58167</v>
+        <v>57144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm, Sylbergen, Ramnäs, Vstm, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558379</v>
+        <v>558224</v>
       </c>
       <c r="R17" t="n">
-        <v>6632329</v>
+        <v>6632361</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2599,22 +2556,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2020-03-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2020-03-25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2629,6 +2586,11 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Tall och gran på hällmark</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2645,16 +2607,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135762156</t>
+          <t>https://artportalen.se/Sighting/83846738</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>100674012</v>
+        <v>102829427</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>58439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2662,46 +2624,61 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm , Vstm</t>
+          <t>Målsjövägen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558313</v>
+        <v>558653</v>
       </c>
       <c r="R18" t="n">
-        <v>6632370</v>
+        <v>6632198</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2725,12 +2702,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,18 +2726,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gran/tallskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2764,66 +2745,70 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100674012</t>
+          <t>https://artportalen.se/Sighting/102829427</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>100674013</v>
+        <v>132490733</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>58136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm , Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm, Sylbergen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558209</v>
+        <v>558136</v>
       </c>
       <c r="R19" t="n">
-        <v>6632406</v>
+        <v>6632414</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2847,12 +2832,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2861,18 +2856,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Gran/tallskog</t>
+          <t>Häll- och blockskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2889,63 +2878,63 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100674013</t>
+          <t>https://artportalen.se/Sighting/132490733</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>100674014</v>
+        <v>135762156</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>58167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm , Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm, Sylbergen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558175</v>
+        <v>558379</v>
       </c>
       <c r="R20" t="n">
-        <v>6632405</v>
+        <v>6632329</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2969,12 +2958,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2983,18 +2982,12 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Gran/tallskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3011,16 +3004,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100674014</t>
+          <t>https://artportalen.se/Sighting/135762156</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135779481</v>
+        <v>100674012</v>
       </c>
       <c r="B21" t="n">
-        <v>56872</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3028,21 +3021,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205995</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3051,27 +3044,23 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558382</v>
+        <v>558313</v>
       </c>
       <c r="R21" t="n">
-        <v>6632335</v>
+        <v>6632370</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3095,27 +3084,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Registrerad med autobox (384 kHz) i skogsmiljö i Sylbergen. Inspelningarna analyserades med BTO Acoustic Pipeline. Dvärgpipistrell registrerades vid flera tillfällen. De starkaste registreringarna gjordes den 8 augusti kl. 00:19 med hög klassificeringssäkerhet och den 7 augusti kl. 21:56.</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3124,12 +3098,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Gran/tallskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3146,63 +3126,63 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135779481</t>
+          <t>https://artportalen.se/Sighting/100674012</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135779311</v>
+        <v>100674013</v>
       </c>
       <c r="B22" t="n">
-        <v>56851</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205998</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558382</v>
+        <v>558209</v>
       </c>
       <c r="R22" t="n">
-        <v>6632335</v>
+        <v>6632406</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3226,27 +3206,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Registrerad med autobox (384 kHz) i skogsmiljö i Sylbergen. Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid flera tillfällen. Den starkaste registreringen gjordes den 8 augusti kl. 01:55 med hög klassificeringssäkerhet och arten registrerades även efterföljande natt.</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3255,12 +3220,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gran/tallskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3277,38 +3248,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135779311</t>
+          <t>https://artportalen.se/Sighting/100674013</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135779178</v>
+        <v>100674014</v>
       </c>
       <c r="B23" t="n">
-        <v>56874</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206002</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3317,27 +3288,23 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558382</v>
+        <v>558175</v>
       </c>
       <c r="R23" t="n">
-        <v>6632335</v>
+        <v>6632405</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3361,27 +3328,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Registrerad med autobox (384 kHz) i skogsmiljö i Sylbergen. Inspelningen analyserades med BTO Acoustic Pipeline. Brunlångöra registrerades vid två skilda tillfällen den 8:e augusti med hög klassificeringssäkerhet.</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3390,12 +3342,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Gran/tallskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3412,62 +3370,59 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135779178</t>
+          <t>https://artportalen.se/Sighting/100674014</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135436864</v>
+        <v>137037411</v>
       </c>
       <c r="B24" t="n">
-        <v>99293</v>
+        <v>8463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs sn, Vstm</t>
+          <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558446</v>
+        <v>558565</v>
       </c>
       <c r="R24" t="n">
-        <v>6632157</v>
+        <v>6632294</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3491,22 +3446,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,76 +3464,91 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135436864</t>
+          <t>https://artportalen.se/Sighting/137037411</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135436981</v>
+        <v>135779481</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>56872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>205995</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs sn, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558469</v>
+        <v>558382</v>
       </c>
       <c r="R25" t="n">
-        <v>6632156</v>
+        <v>6632335</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3612,22 +3572,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz) i skogsmiljö i Sylbergen. Inspelningarna analyserades med BTO Acoustic Pipeline. Dvärgpipistrell registrerades vid flera tillfällen. De starkaste registreringarna gjordes den 8 augusti kl. 00:19 med hög klassificeringssäkerhet och den 7 augusti kl. 21:56.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3636,23 +3601,535 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135779481</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135779311</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56851</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sylbergen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>558382</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6632335</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz) i skogsmiljö i Sylbergen. Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid flera tillfällen. Den starkaste registreringen gjordes den 8 augusti kl. 01:55 med hög klassificeringssäkerhet och arten registrerades även efterföljande natt.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135779311</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135779178</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56874</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sylbergen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>558382</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6632335</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz) i skogsmiljö i Sylbergen. Inspelningen analyserades med BTO Acoustic Pipeline. Brunlångöra registrerades vid två skilda tillfällen den 8:e augusti med hög klassificeringssäkerhet.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135779178</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135436864</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sylbergen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>558446</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6632157</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135436864</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135436981</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sylbergen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>558469</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6632156</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135436981</t>
         </is>
@@ -3684,6 +4161,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>137037411</v>
       </c>
       <c r="B24" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>137037411</v>
       </c>
       <c r="B24" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>137037851</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>137037232</v>
       </c>
       <c r="B13" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>137037708</v>
       </c>
       <c r="B14" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
